--- a/outputs/daily/hr_rankings_2026-07-19_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-19_remaining.xlsx
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>57.6</v>
+        <v>56.2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>97</v>
+        <v>94.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -13431,27 +13431,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>695670</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Harry Ford</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-20T23:05:00Z</t>
+          <t>2026-07-21T00:40:00Z</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -13461,22 +13461,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Braxton Ashcraft</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>677952</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -13494,26 +13494,26 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>50.8</v>
+        <v>35.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>30.1</v>
+        <v>61.8</v>
       </c>
       <c r="R48" t="n">
-        <v>38.2</v>
+        <v>38.7</v>
       </c>
       <c r="S48" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T48" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U48" t="n">
-        <v>54.7</v>
+        <v>56.6</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -13564,139 +13564,139 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 2 games</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.5% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>101.1264</t>
+          <t>96.3391</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>0.4679</t>
+          <t>0.2995</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.2122</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.253</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>61.69</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>44.78</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.4898</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>0.1255</t>
+          <t>0.1994</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr"/>
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr"/>
@@ -13707,27 +13707,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>695670</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Harry Ford</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-21T00:40:00Z</t>
+          <t>2026-07-20T23:05:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -13737,26 +13737,26 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Braxton Ashcraft</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>677952</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13770,26 +13770,26 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>35.1</v>
+        <v>50.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>61.8</v>
+        <v>30.1</v>
       </c>
       <c r="R49" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="S49" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T49" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U49" t="n">
-        <v>56.6</v>
+        <v>52</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -13840,139 +13840,139 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 2 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.5% barrel, 19.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>11.82</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>96.3391</t>
+          <t>101.1264</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.2995</t>
+          <t>0.4679</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.2122</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>61.69</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.4898</t>
+          <t>0.3542</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1994</t>
+          <t>0.1255</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr"/>
       <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -18951,27 +18951,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>643217</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Andrew Benintendi</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -18981,22 +18981,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -19014,26 +19014,26 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>38.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>35.9</v>
+        <v>49.8</v>
       </c>
       <c r="R68" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S68" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T68" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U68" t="n">
-        <v>50.3</v>
+        <v>26.1</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -19089,134 +19089,134 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 5/17, 0 HR</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 19.0 HR allowed</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>10.05</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>42.59</t>
+          <t>45.02</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>100.2268</t>
+          <t>98.9931</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4328</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.1837</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>72.88</t>
+          <t>69.54</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>52.48</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.37</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1665</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr"/>
       <c r="BH68" t="inlineStr"/>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr"/>
@@ -19227,27 +19227,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>643217</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Andrew Benintendi</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-21T00:05:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -19257,26 +19257,26 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -19290,26 +19290,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>40.8</v>
+        <v>38.9</v>
       </c>
       <c r="Q69" t="n">
-        <v>49.8</v>
+        <v>35.9</v>
       </c>
       <c r="R69" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S69" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T69" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U69" t="n">
-        <v>26.1</v>
+        <v>48.1</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19365,134 +19365,134 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 7/22, 1 HR</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 19.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>45.02</t>
+          <t>42.59</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>98.9931</t>
+          <t>100.2268</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.4328</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1837</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>69.54</t>
+          <t>72.88</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>52.48</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1665</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr"/>
       <c r="BH69" t="inlineStr"/>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -24747,27 +24747,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>671218</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Heliot Ramos</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-20T23:40:00Z</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -24777,22 +24777,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -24810,26 +24810,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>47</v>
+        <v>54.9</v>
       </c>
       <c r="Q89" t="n">
-        <v>35.9</v>
+        <v>35.1</v>
       </c>
       <c r="R89" t="n">
-        <v>34.3</v>
+        <v>23.2</v>
       </c>
       <c r="S89" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T89" t="n">
         <v>50</v>
       </c>
       <c r="U89" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -24885,12 +24885,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -24900,119 +24900,119 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 8/30, 0 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>45.14</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>92.29</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>100.8553</t>
+          <t>103.2576</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.4894</t>
+          <t>0.4674</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2023</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.334</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>23.86</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.1986</t>
+          <t>0.1734</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.413</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1605</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>27.48</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25023,22 +25023,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>671218</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Heliot Ramos</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -25053,17 +25053,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25086,26 +25086,26 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>54.9</v>
+        <v>39.9</v>
       </c>
       <c r="Q90" t="n">
-        <v>35.1</v>
+        <v>31.8</v>
       </c>
       <c r="R90" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S90" t="n">
-        <v>81.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T90" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U90" t="n">
-        <v>22</v>
+        <v>40.9</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
@@ -25161,134 +25161,134 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/30, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 16.8 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>92.29</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>103.2576</t>
+          <t>100.6415</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.4674</t>
+          <t>0.4381</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.2023</t>
+          <t>0.1817</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.3427</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>72.74</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>12.22</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1734</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>0.3624</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.1605</t>
+          <t>0.1382</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>27.48</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BG90" t="inlineStr"/>
       <c r="BH90" t="inlineStr"/>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25299,27 +25299,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666160</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Mickey Moniak</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-20T23:40:00Z</t>
+          <t>2026-07-21T00:40:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -25329,22 +25329,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -25362,26 +25362,26 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>39.9</v>
+        <v>52.7</v>
       </c>
       <c r="Q91" t="n">
-        <v>31.8</v>
+        <v>21.8</v>
       </c>
       <c r="R91" t="n">
-        <v>27.6</v>
+        <v>38.7</v>
       </c>
       <c r="S91" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T91" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U91" t="n">
-        <v>40.9</v>
+        <v>16.6</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -25437,134 +25437,134 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 16.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>100.6415</t>
+          <t>100.6203</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.4381</t>
+          <t>0.4592</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.1817</t>
+          <t>0.2196</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3427</t>
+          <t>0.3188</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>74.15</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.2746</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.3624</t>
+          <t>0.3479</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.1382</t>
+          <t>0.1046</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr"/>
       <c r="BH91" t="inlineStr"/>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -25575,27 +25575,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>666160</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mickey Moniak</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-21T00:40:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -25605,17 +25605,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -25624,7 +25624,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -25642,22 +25642,22 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>52.7</v>
+        <v>47</v>
       </c>
       <c r="Q92" t="n">
-        <v>21.8</v>
+        <v>35.9</v>
       </c>
       <c r="R92" t="n">
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="S92" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T92" t="n">
         <v>50</v>
       </c>
       <c r="U92" t="n">
-        <v>16.6</v>
+        <v>7</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
@@ -25713,12 +25713,12 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -25728,72 +25728,72 @@
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>45.14</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>100.6203</t>
+          <t>100.8553</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
         <is>
-          <t>0.4592</t>
+          <t>0.4894</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>0.2196</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>0.3188</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>74.15</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -25803,44 +25803,44 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>0.2746</t>
+          <t>0.1986</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD92" t="inlineStr">
         <is>
-          <t>0.3479</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
-          <t>0.1046</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BF92" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="BG92" t="inlineStr"/>
       <c r="BH92" t="inlineStr"/>
       <c r="BI92" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ92" t="inlineStr"/>
@@ -26403,27 +26403,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>665489</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Vladimir Guerrero</t>
+          <t>Jazz Chisholm</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-20T23:07:00Z</t>
+          <t>2026-07-20T23:05:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -26433,17 +26433,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Braxton Ashcraft</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>677952</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -26466,26 +26466,26 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>40.9</v>
+        <v>42.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>35.5</v>
+        <v>30.1</v>
       </c>
       <c r="R95" t="n">
-        <v>30.4</v>
+        <v>38.2</v>
       </c>
       <c r="S95" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T95" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U95" t="n">
-        <v>57.6</v>
+        <v>53.3</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -26541,12 +26541,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26571,104 +26571,104 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>90.67</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>103.2609</t>
+          <t>100.3793</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.3977</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1486</t>
+          <t>0.1805</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.3588</t>
+          <t>0.3075</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>76.28</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>63.43</t>
+          <t>34.41</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>52.68</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.1907</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.4338</t>
+          <t>0.3542</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.1255</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr"/>
       <c r="BH95" t="inlineStr"/>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -26679,27 +26679,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>665489</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Vladimir Guerrero</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-21T00:05:00Z</t>
+          <t>2026-07-20T23:07:00Z</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -26709,17 +26709,17 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -26742,26 +26742,26 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>26.2</v>
+        <v>40.9</v>
       </c>
       <c r="Q96" t="n">
-        <v>49.8</v>
+        <v>35.5</v>
       </c>
       <c r="R96" t="n">
-        <v>27.6</v>
+        <v>30.4</v>
       </c>
       <c r="S96" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T96" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U96" t="n">
-        <v>46.4</v>
+        <v>57.6</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -26800,7 +26800,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr"/>
@@ -26817,7 +26817,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
@@ -26837,114 +26837,114 @@
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 19.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>46.57</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>90.67</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>98.3371</t>
+          <t>103.2609</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.1486</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>0.3588</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>76.28</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>63.43</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1204</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD96" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4338</t>
         </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
-          <t>0.1665</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BG96" t="inlineStr"/>
       <c r="BH96" t="inlineStr"/>
       <c r="BI96" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ96" t="inlineStr"/>
@@ -26955,27 +26955,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-20T23:40:00Z</t>
+          <t>2026-07-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -26990,12 +26990,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Trevor McDonald</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>686790</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -27004,7 +27004,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -27018,17 +27018,17 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>53.4</v>
+        <v>26.2</v>
       </c>
       <c r="Q97" t="n">
-        <v>20.3</v>
+        <v>49.8</v>
       </c>
       <c r="R97" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S97" t="n">
         <v>88.7</v>
@@ -27037,7 +27037,7 @@
         <v>80</v>
       </c>
       <c r="U97" t="n">
-        <v>18</v>
+        <v>46.4</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -27093,134 +27093,134 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.1% barrel, 4.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 19.0 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>47.73</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>92.04</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>102.8609</t>
+          <t>98.3371</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.4468</t>
+          <t>0.433</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.1976</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.2073</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>9.02</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>43.37</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>0.3571</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.1665</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>16.74</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="BG97" t="inlineStr"/>
       <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -27231,27 +27231,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>672356</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Gabriel Arias</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-20T22:40:00Z</t>
+          <t>2026-07-20T23:40:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -27261,17 +27261,17 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Trevor McDonald</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>686790</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -27280,7 +27280,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -27294,26 +27294,26 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>45.9</v>
+        <v>53.4</v>
       </c>
       <c r="Q98" t="n">
-        <v>49.8</v>
+        <v>20.3</v>
       </c>
       <c r="R98" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S98" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T98" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U98" t="n">
-        <v>43.2</v>
+        <v>18</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -27374,129 +27374,129 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.1% barrel, 4.5 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>47.73</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>91.11</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>103.0932</t>
+          <t>102.8609</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.4032</t>
+          <t>0.4468</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.1794</t>
+          <t>0.1976</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.2874</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>36.52</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>29.51</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.1654</t>
+          <t>0.2073</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>89.71</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3571</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>16.74</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr"/>
       <c r="BH98" t="inlineStr"/>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -27507,27 +27507,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>656811</t>
+          <t>672356</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ryan O'Hearn</t>
+          <t>Gabriel Arias</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-20T23:05:00Z</t>
+          <t>2026-07-20T22:40:00Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -27537,26 +27537,26 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>657746</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -27570,26 +27570,26 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>37.2</v>
+        <v>45.9</v>
       </c>
       <c r="Q99" t="n">
-        <v>50.8</v>
+        <v>49.8</v>
       </c>
       <c r="R99" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S99" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T99" t="n">
         <v>50</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>43.2</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -27645,27 +27645,27 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 0 HR</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 13.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
@@ -27675,104 +27675,104 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>7.81</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>47.36</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>91.11</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>99.5988</t>
+          <t>103.0932</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.4246</t>
+          <t>0.4032</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1642</t>
+          <t>0.1794</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.3323</t>
+          <t>0.2874</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>36.52</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.1654</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.71</t>
         </is>
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>0.4327</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
-          <t>0.1848</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>29.33</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr"/>
       <c r="BH99" t="inlineStr"/>
       <c r="BI99" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ99" t="inlineStr"/>
@@ -27783,27 +27783,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>676551</t>
+          <t>656811</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brewer Hicklen</t>
+          <t>Ryan O'Hearn</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-20T23:15:00Z</t>
+          <t>2026-07-20T23:05:00Z</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -27813,17 +27813,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>JP Sears</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>676664</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -27832,7 +27832,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -27846,26 +27846,26 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>40.2</v>
+        <v>37.2</v>
       </c>
       <c r="Q100" t="n">
-        <v>55.2</v>
+        <v>50.8</v>
       </c>
       <c r="R100" t="n">
-        <v>30.9</v>
+        <v>38.2</v>
       </c>
       <c r="S100" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T100" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U100" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
@@ -27916,17 +27916,17 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -27936,119 +27936,119 @@
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Contact streak: 5/11 over last 3 games</t>
+          <t>Last 7 games: 2/22, 0 HR</t>
         </is>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 11.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>7.81</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>89.68</t>
         </is>
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>103.1078</t>
+          <t>99.5988</t>
         </is>
       </c>
       <c r="AR100" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.4246</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>0.1114</t>
+          <t>0.1642</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>0.3089</t>
+          <t>0.3323</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>72.11</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>45.07</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD100" t="inlineStr">
         <is>
-          <t>0.4621</t>
+          <t>0.4327</t>
         </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
-          <t>0.1966</t>
+          <t>0.1848</t>
         </is>
       </c>
       <c r="BF100" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="BG100" t="inlineStr"/>
       <c r="BH100" t="inlineStr"/>
       <c r="BI100" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ100" t="inlineStr"/>
@@ -28059,27 +28059,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>676551</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Brewer Hicklen</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-20T23:15:00Z</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -28089,17 +28089,17 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>JP Sears</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>676664</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -28108,7 +28108,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -28126,22 +28126,22 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>39.2</v>
+        <v>40.2</v>
       </c>
       <c r="Q101" t="n">
-        <v>35.9</v>
+        <v>55.2</v>
       </c>
       <c r="R101" t="n">
-        <v>34.3</v>
+        <v>30.9</v>
       </c>
       <c r="S101" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T101" t="n">
         <v>78</v>
       </c>
       <c r="U101" t="n">
-        <v>14.6</v>
+        <v>45</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed; order MLB 5 vs RotoWire 8</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -28192,7 +28192,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
@@ -28202,7 +28202,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -28212,119 +28212,119 @@
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Contact streak: 5/11 over last 3 games</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 11.8 HR allowed</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>101.5962</t>
+          <t>103.1078</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>0.1528</t>
+          <t>0.1114</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>0.2866</t>
+          <t>0.3089</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>74.08</t>
+          <t>72.11</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>0.1678</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>45.07</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="BD101" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.4621</t>
         </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1966</t>
         </is>
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="BG101" t="inlineStr"/>
       <c r="BH101" t="inlineStr"/>
       <c r="BI101" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ101" t="inlineStr"/>
@@ -28335,22 +28335,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>694212</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -28370,12 +28370,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -28384,7 +28384,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -28398,26 +28398,26 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>49.9</v>
+        <v>39.2</v>
       </c>
       <c r="Q102" t="n">
-        <v>30</v>
+        <v>35.9</v>
       </c>
       <c r="R102" t="n">
-        <v>28.7</v>
+        <v>34.3</v>
       </c>
       <c r="S102" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="T102" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U102" t="n">
-        <v>37.4</v>
+        <v>14.6</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -28451,7 +28451,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>lineup projected / unconfirmed; order MLB 5 vs RotoWire 8</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -28473,27 +28473,27 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 7.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
@@ -28503,104 +28503,104 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>44.96</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>102.5297</t>
+          <t>101.5962</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>0.4422</t>
+          <t>0.3663</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>0.2029</t>
+          <t>0.1528</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.3204</t>
+          <t>0.2866</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>74.87</t>
+          <t>74.08</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>0.1965</t>
+          <t>0.1678</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>0.3637</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr"/>
       <c r="BH102" t="inlineStr"/>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr"/>
@@ -28611,27 +28611,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>694212</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-21T01:40:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -28641,17 +28641,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -28674,26 +28674,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>23.4</v>
+        <v>49.9</v>
       </c>
       <c r="Q103" t="n">
-        <v>58.6</v>
+        <v>30</v>
       </c>
       <c r="R103" t="n">
-        <v>28.2</v>
+        <v>28.7</v>
       </c>
       <c r="S103" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T103" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U103" t="n">
-        <v>8.800000000000001</v>
+        <v>37.4</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -28732,7 +28732,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr"/>
@@ -28749,134 +28749,134 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.0% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 7.1 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>11.77</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>44.96</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>97.861</t>
+          <t>102.5297</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.3761</t>
+          <t>0.4422</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.1466</t>
+          <t>0.2029</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.3204</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>74.87</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>42.46</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.1848</t>
+          <t>0.1965</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.3637</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr"/>
       <c r="BH103" t="inlineStr"/>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -28887,27 +28887,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-20T23:05:00Z</t>
+          <t>2026-07-21T01:40:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -28917,26 +28917,26 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Braxton Ashcraft</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>677952</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -28950,26 +28950,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>42.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q104" t="n">
-        <v>30.1</v>
+        <v>58.6</v>
       </c>
       <c r="R104" t="n">
-        <v>38.2</v>
+        <v>28.2</v>
       </c>
       <c r="S104" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T104" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U104" t="n">
-        <v>30.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29008,7 +29008,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr"/>
@@ -29030,129 +29030,129 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>100.3793</t>
+          <t>97.861</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3977</t>
+          <t>0.3761</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1805</t>
+          <t>0.1466</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.3075</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>34.41</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>52.68</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1907</t>
+          <t>0.1848</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.481</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1255</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr"/>
       <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -31095,27 +31095,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>596019</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Francisco Lindor</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-20T23:05:00Z</t>
+          <t>2026-07-20T23:40:00Z</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -31130,12 +31130,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Braxton Ashcraft</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>677952</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -31162,22 +31162,22 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>30.2</v>
+        <v>43.9</v>
       </c>
       <c r="Q112" t="n">
-        <v>30.1</v>
+        <v>16.2</v>
       </c>
       <c r="R112" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S112" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T112" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U112" t="n">
-        <v>42</v>
+        <v>59.6</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -31233,27 +31233,27 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.6% barrel, 8.7 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -31263,104 +31263,104 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>88.79</t>
+          <t>91.48</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>98.5451</t>
+          <t>100.3117</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.4365</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.1835</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.3352</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.2768</t>
         </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
-          <t>0.1255</t>
+          <t>0.0975</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr"/>
       <c r="BH112" t="inlineStr"/>
       <c r="BI112" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ112" t="inlineStr"/>
@@ -31371,27 +31371,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>596019</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Francisco Lindor</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-20T23:40:00Z</t>
+          <t>2026-07-21T00:40:00Z</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -31401,22 +31401,22 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -31434,26 +31434,26 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>43.9</v>
+        <v>30.2</v>
       </c>
       <c r="Q113" t="n">
-        <v>16.2</v>
+        <v>61.8</v>
       </c>
       <c r="R113" t="n">
-        <v>27.6</v>
+        <v>38.7</v>
       </c>
       <c r="S113" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T113" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U113" t="n">
-        <v>59.6</v>
+        <v>28.1</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -31509,27 +31509,27 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.6% barrel, 8.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.5% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -31539,104 +31539,104 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>91.48</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>100.3117</t>
+          <t>98.6513</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>0.4365</t>
+          <t>0.4259</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>0.1835</t>
+          <t>0.1558</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>0.3352</t>
+          <t>0.3263</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>41.01</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1703</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>44.78</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>0.2768</t>
+          <t>0.4898</t>
         </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
-          <t>0.0975</t>
+          <t>0.1994</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr"/>
       <c r="BH113" t="inlineStr"/>
       <c r="BI113" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ113" t="inlineStr"/>
@@ -31647,27 +31647,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-21T00:40:00Z</t>
+          <t>2026-07-20T23:05:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -31677,26 +31677,26 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Braxton Ashcraft</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>677952</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -31710,26 +31710,26 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P114" t="n">
         <v>30.2</v>
       </c>
       <c r="Q114" t="n">
-        <v>61.8</v>
+        <v>30.1</v>
       </c>
       <c r="R114" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
       <c r="S114" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T114" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U114" t="n">
-        <v>28.1</v>
+        <v>39.7</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -31785,27 +31785,27 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 10/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.5% barrel, 19.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -31815,104 +31815,104 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.79</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>98.6513</t>
+          <t>98.5451</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.4259</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.1558</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.3263</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>31.57</t>
+          <t>32.13</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.1703</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.4898</t>
+          <t>0.3542</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1994</t>
+          <t>0.1255</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr"/>
       <c r="BH114" t="inlineStr"/>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -31923,27 +31923,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>608324</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Alex Bregman</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -31958,17 +31958,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Jack Flaherty</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>656427</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -31986,26 +31986,26 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>33.8</v>
+        <v>24</v>
       </c>
       <c r="Q115" t="n">
-        <v>35.9</v>
+        <v>48.9</v>
       </c>
       <c r="R115" t="n">
-        <v>34.3</v>
+        <v>29.8</v>
       </c>
       <c r="S115" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T115" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U115" t="n">
-        <v>3.4</v>
+        <v>70.3</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -32061,134 +32061,134 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.0% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>98.5765</t>
+          <t>98.2351</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.3752</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>69.28</t>
+          <t>70.16</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1697</t>
+          <t>0.1386</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.3948</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1597</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
       <c r="BH115" t="inlineStr"/>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr"/>
@@ -32199,27 +32199,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>608324</t>
+          <t>691723</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Alex Bregman</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-21T00:05:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -32229,26 +32229,26 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Jack Flaherty</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>656427</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="M116" t="inlineStr">
         <is>
@@ -32262,26 +32262,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>24</v>
+        <v>45.9</v>
       </c>
       <c r="Q116" t="n">
-        <v>48.9</v>
+        <v>30</v>
       </c>
       <c r="R116" t="n">
-        <v>29.8</v>
+        <v>28.7</v>
       </c>
       <c r="S116" t="n">
-        <v>90.40000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T116" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U116" t="n">
-        <v>70.3</v>
+        <v>87</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -32337,12 +32337,12 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -32357,7 +32357,7 @@
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.0% barrel, 13.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 7.1 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
@@ -32367,57 +32367,57 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>90.73</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>98.2351</t>
+          <t>103.0252</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.3752</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.2932</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>70.16</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>50.39</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -32427,44 +32427,44 @@
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.1386</t>
+          <t>0.1892</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3948</t>
+          <t>0.3637</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.1597</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -32475,22 +32475,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>691723</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -32505,17 +32505,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32538,26 +32538,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>45.9</v>
+        <v>33.8</v>
       </c>
       <c r="Q117" t="n">
-        <v>30</v>
+        <v>35.9</v>
       </c>
       <c r="R117" t="n">
-        <v>28.7</v>
+        <v>34.3</v>
       </c>
       <c r="S117" t="n">
-        <v>47.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T117" t="n">
         <v>78</v>
       </c>
       <c r="U117" t="n">
-        <v>87</v>
+        <v>1.6</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -32613,134 +32613,134 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 7.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>38.04</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>90.73</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>103.0252</t>
+          <t>98.5765</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.2932</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>50.39</t>
+          <t>39.82</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1892</t>
+          <t>0.1697</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.3637</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -33456,7 +33456,7 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Last 7 games: 2/24, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
@@ -35235,27 +35235,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>691176</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jasson Dominguez</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-20T23:05:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -35265,17 +35265,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Braxton Ashcraft</t>
+          <t>Emmet Sheehan</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>677952</t>
+          <t>686218</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -35298,26 +35298,26 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>28</v>
+        <v>27.3</v>
       </c>
       <c r="Q127" t="n">
-        <v>29</v>
+        <v>45.6</v>
       </c>
       <c r="R127" t="n">
-        <v>38.2</v>
+        <v>34.3</v>
       </c>
       <c r="S127" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T127" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U127" t="n">
-        <v>39.2</v>
+        <v>24</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35351,7 +35351,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed; order MLB 3 vs RotoWire 5</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -35378,22 +35378,22 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 1 HR</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -35403,104 +35403,104 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>35.73</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>100.8327</t>
+          <t>98.5353</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.3791</t>
+          <t>0.4021</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.3046</t>
+          <t>0.3165</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>74.17</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1632</t>
+          <t>0.1424</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>40.06</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.3831</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1255</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr"/>
       <c r="BH127" t="inlineStr"/>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -35511,27 +35511,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Cole Young</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-21T01:40:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -35541,22 +35541,22 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Emmet Sheehan</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>686218</t>
+          <t>671096</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -35574,26 +35574,26 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>27.3</v>
+        <v>25.7</v>
       </c>
       <c r="Q128" t="n">
-        <v>45.6</v>
+        <v>41.1</v>
       </c>
       <c r="R128" t="n">
-        <v>34.3</v>
+        <v>25.4</v>
       </c>
       <c r="S128" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T128" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U128" t="n">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -35659,17 +35659,17 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -35679,104 +35679,104 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>35.73</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>88.16</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>98.5353</t>
+          <t>98.9687</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.4021</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>69.82</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.1424</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>40.06</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>0.3831</t>
+          <t>0.4137</t>
         </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.1632</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr"/>
       <c r="BH128" t="inlineStr"/>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr"/>
@@ -35787,27 +35787,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>691176</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cole Young</t>
+          <t>Jasson Dominguez</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-21T01:40:00Z</t>
+          <t>2026-07-20T23:05:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -35822,21 +35822,21 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Braxton Ashcraft</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>671096</t>
+          <t>677952</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -35850,26 +35850,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>25.7</v>
+        <v>28</v>
       </c>
       <c r="Q129" t="n">
-        <v>41.1</v>
+        <v>29</v>
       </c>
       <c r="R129" t="n">
-        <v>25.4</v>
+        <v>38.2</v>
       </c>
       <c r="S129" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T129" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U129" t="n">
-        <v>79</v>
+        <v>37.8</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -35903,7 +35903,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>lineup projected / unconfirmed; order MLB 3 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -35930,22 +35930,22 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 16.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.6% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -35955,104 +35955,104 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>88.16</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>98.9687</t>
+          <t>100.8327</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.3791</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.3046</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>74.17</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1632</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.4137</t>
+          <t>0.3542</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1632</t>
+          <t>0.1255</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr"/>
       <c r="BH129" t="inlineStr"/>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -48207,27 +48207,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>805347</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-20T23:15:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -48242,12 +48242,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>JP Sears</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>676664</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -48274,13 +48274,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>43.9</v>
+        <v>24.1</v>
       </c>
       <c r="Q174" t="n">
-        <v>35.9</v>
+        <v>55.2</v>
       </c>
       <c r="R174" t="n">
-        <v>34.3</v>
+        <v>30.9</v>
       </c>
       <c r="S174" t="n">
         <v>47.9</v>
@@ -48289,7 +48289,7 @@
         <v>50</v>
       </c>
       <c r="U174" t="n">
-        <v>4.5</v>
+        <v>52.5</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr"/>
@@ -48345,134 +48345,134 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Contact streak: 8/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.8 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>101.5901</t>
+          <t>97.3709</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.4091</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.1732</t>
+          <t>0.117</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.278</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>17.61</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.1879</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>45.07</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.4621</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1966</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -48483,27 +48483,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>805347</t>
+          <t>608348</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-07-20T23:15:00Z</t>
+          <t>2026-07-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -48518,21 +48518,21 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>JP Sears</t>
+          <t>Jack Flaherty</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>676664</t>
+          <t>656427</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -48546,17 +48546,17 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>24.1</v>
+        <v>30.4</v>
       </c>
       <c r="Q175" t="n">
-        <v>55.2</v>
+        <v>48.9</v>
       </c>
       <c r="R175" t="n">
-        <v>30.9</v>
+        <v>29.8</v>
       </c>
       <c r="S175" t="n">
         <v>47.9</v>
@@ -48565,7 +48565,7 @@
         <v>50</v>
       </c>
       <c r="U175" t="n">
-        <v>52.5</v>
+        <v>42.7</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr"/>
@@ -48621,134 +48621,134 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.0% barrel, 13.2 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>38.76</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>97.3709</t>
+          <t>99.1684</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.1575</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>0.3252</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>25.15</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.1412</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>45.07</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.4621</t>
+          <t>0.3948</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.1966</t>
+          <t>0.1597</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
       <c r="BH175" t="inlineStr"/>
       <c r="BI175" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ175" t="inlineStr"/>
@@ -48808,7 +48808,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="M176" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>50</v>
       </c>
       <c r="U176" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="V176" t="inlineStr">
         <is>
@@ -48902,7 +48902,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ176" t="inlineStr">
@@ -48912,7 +48912,7 @@
       </c>
       <c r="AK176" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL176" t="inlineStr">
@@ -49035,27 +49035,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>608348</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-07-21T00:05:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -49070,21 +49070,21 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Jack Flaherty</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>656427</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -49098,17 +49098,17 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P177" t="n">
-        <v>30.4</v>
+        <v>43.9</v>
       </c>
       <c r="Q177" t="n">
-        <v>48.9</v>
+        <v>35.9</v>
       </c>
       <c r="R177" t="n">
-        <v>29.8</v>
+        <v>34.3</v>
       </c>
       <c r="S177" t="n">
         <v>47.9</v>
@@ -49117,7 +49117,7 @@
         <v>50</v>
       </c>
       <c r="U177" t="n">
-        <v>42.7</v>
+        <v>0</v>
       </c>
       <c r="V177" t="inlineStr">
         <is>
@@ -49173,27 +49173,27 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 0/15, 0 HR</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.0% barrel, 13.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
@@ -49203,104 +49203,104 @@
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>38.76</t>
+          <t>43.76</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>99.1684</t>
+          <t>101.5901</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4091</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>0.1575</t>
+          <t>0.1732</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>0.3252</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>17.61</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>0.1412</t>
+          <t>0.1879</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>0.3948</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="BE177" t="inlineStr">
         <is>
-          <t>0.1597</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="BG177" t="inlineStr"/>
       <c r="BH177" t="inlineStr"/>
       <c r="BI177" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ177" t="inlineStr"/>
@@ -53451,27 +53451,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>669699</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Braden Shewmake</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-07-20T23:40:00Z</t>
+          <t>2026-07-20T23:10:00Z</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -53481,26 +53481,26 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -53518,22 +53518,22 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>32.1</v>
+        <v>27.4</v>
       </c>
       <c r="Q193" t="n">
-        <v>31.8</v>
+        <v>34.7</v>
       </c>
       <c r="R193" t="n">
-        <v>27.6</v>
+        <v>34.3</v>
       </c>
       <c r="S193" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T193" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U193" t="n">
-        <v>28.2</v>
+        <v>59</v>
       </c>
       <c r="V193" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
@@ -53572,7 +53572,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr"/>
@@ -53589,27 +53589,27 @@
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/13, 0 HR</t>
+          <t>Contact streak: 9/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.6% barrel, 16.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
@@ -53619,104 +53619,104 @@
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>89.14</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
         <is>
-          <t>98.7011</t>
+          <t>100.1334</t>
         </is>
       </c>
       <c r="AR193" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1265</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.55</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>12.98</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1472</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>87.86</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD193" t="inlineStr">
         <is>
-          <t>0.3624</t>
+          <t>0.3611</t>
         </is>
       </c>
       <c r="BE193" t="inlineStr">
         <is>
-          <t>0.1382</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>18.09</t>
         </is>
       </c>
       <c r="BG193" t="inlineStr"/>
       <c r="BH193" t="inlineStr"/>
       <c r="BI193" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ193" t="inlineStr"/>
@@ -53727,27 +53727,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>669699</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Braden Shewmake</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-07-21T01:40:00Z</t>
+          <t>2026-07-20T23:40:00Z</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -53757,22 +53757,22 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>671096</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L194" t="n">
@@ -53790,26 +53790,26 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P194" t="n">
-        <v>24.8</v>
+        <v>32.1</v>
       </c>
       <c r="Q194" t="n">
-        <v>41.1</v>
+        <v>31.8</v>
       </c>
       <c r="R194" t="n">
-        <v>25.4</v>
+        <v>27.6</v>
       </c>
       <c r="S194" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T194" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U194" t="n">
-        <v>25.8</v>
+        <v>28.2</v>
       </c>
       <c r="V194" t="inlineStr">
         <is>
@@ -53823,7 +53823,7 @@
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
@@ -53848,7 +53848,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr"/>
@@ -53865,12 +53865,12 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
@@ -53880,12 +53880,12 @@
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 4/13, 0 HR</t>
         </is>
       </c>
       <c r="AL194" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.6% barrel, 16.8 HR allowed</t>
         </is>
       </c>
       <c r="AM194" t="inlineStr">
@@ -53895,104 +53895,104 @@
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
         <is>
-          <t>99.279</t>
+          <t>98.7011</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
         <is>
-          <t>0.4066</t>
+          <t>0.417</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>0.1366</t>
+          <t>0.169</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr">
         <is>
-          <t>0.3245</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>11.32</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>0.1201</t>
+          <t>0.169</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>87.86</t>
         </is>
       </c>
       <c r="BD194" t="inlineStr">
         <is>
-          <t>0.4137</t>
+          <t>0.3624</t>
         </is>
       </c>
       <c r="BE194" t="inlineStr">
         <is>
-          <t>0.1632</t>
+          <t>0.1382</t>
         </is>
       </c>
       <c r="BF194" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BG194" t="inlineStr"/>
       <c r="BH194" t="inlineStr"/>
       <c r="BI194" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ194" t="inlineStr"/>
@@ -54003,27 +54003,27 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>672724</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Oswald Peraza</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-07-21T02:10:00Z</t>
+          <t>2026-07-21T01:40:00Z</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -54033,26 +54033,26 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Kyle Leahy</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>681517</t>
+          <t>671096</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -54073,19 +54073,19 @@
         <v>24.8</v>
       </c>
       <c r="Q195" t="n">
-        <v>55.9</v>
+        <v>41.1</v>
       </c>
       <c r="R195" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="S195" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T195" t="n">
         <v>50</v>
       </c>
       <c r="U195" t="n">
-        <v>12</v>
+        <v>25.8</v>
       </c>
       <c r="V195" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
@@ -54141,12 +54141,12 @@
       </c>
       <c r="AH195" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ195" t="inlineStr">
@@ -54156,12 +54156,12 @@
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL195" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 7.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM195" t="inlineStr">
@@ -54171,104 +54171,104 @@
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.68</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>100.0649</t>
+          <t>99.279</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
         <is>
-          <t>0.3466</t>
+          <t>0.4066</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>0.1232</t>
+          <t>0.1366</t>
         </is>
       </c>
       <c r="AT195" t="inlineStr">
         <is>
-          <t>0.2718</t>
+          <t>0.3245</t>
         </is>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>72.76</t>
+          <t>70.44</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>0.1231</t>
+          <t>0.1201</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>10.57</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>91.06</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="BD195" t="inlineStr">
         <is>
-          <t>0.4513</t>
+          <t>0.4137</t>
         </is>
       </c>
       <c r="BE195" t="inlineStr">
         <is>
-          <t>0.1789</t>
+          <t>0.1632</t>
         </is>
       </c>
       <c r="BF195" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BG195" t="inlineStr"/>
       <c r="BH195" t="inlineStr"/>
       <c r="BI195" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ195" t="inlineStr"/>
@@ -54279,27 +54279,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>543309</t>
+          <t>672724</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Kyle Higashioka</t>
+          <t>Oswald Peraza</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-07-21T00:05:00Z</t>
+          <t>2026-07-21T02:10:00Z</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -54309,17 +54309,17 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Kyle Leahy</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>607200</t>
+          <t>681517</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -54328,7 +54328,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -54346,22 +54346,22 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>30.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q196" t="n">
-        <v>42.3</v>
+        <v>55.9</v>
       </c>
       <c r="R196" t="n">
-        <v>27.6</v>
+        <v>28.2</v>
       </c>
       <c r="S196" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T196" t="n">
         <v>50</v>
       </c>
       <c r="U196" t="n">
-        <v>58.1</v>
+        <v>12</v>
       </c>
       <c r="V196" t="inlineStr">
         <is>
@@ -54375,7 +54375,7 @@
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y196" t="inlineStr">
@@ -54417,27 +54417,27 @@
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/15, 0 HR</t>
         </is>
       </c>
       <c r="AL196" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM196" t="inlineStr">
@@ -54447,104 +54447,104 @@
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
         <is>
-          <t>99.0661</t>
+          <t>100.0649</t>
         </is>
       </c>
       <c r="AR196" t="inlineStr">
         <is>
-          <t>0.3653</t>
+          <t>0.3466</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1232</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr">
         <is>
-          <t>0.2957</t>
+          <t>0.2718</t>
         </is>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>70.97</t>
+          <t>72.76</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>10.79</t>
+          <t>28.32</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>0.1529</t>
+          <t>0.1231</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>10.57</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>48.51</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>89.15</t>
+          <t>91.06</t>
         </is>
       </c>
       <c r="BD196" t="inlineStr">
         <is>
-          <t>0.4344</t>
+          <t>0.4513</t>
         </is>
       </c>
       <c r="BE196" t="inlineStr">
         <is>
-          <t>0.1685</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="BF196" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>22.89</t>
         </is>
       </c>
       <c r="BG196" t="inlineStr"/>
       <c r="BH196" t="inlineStr"/>
       <c r="BI196" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ196" t="inlineStr"/>
@@ -54555,27 +54555,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>666182</t>
+          <t>543309</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bo Bichette</t>
+          <t>Kyle Higashioka</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-07-20T23:40:00Z</t>
+          <t>2026-07-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -54585,17 +54585,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607200</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -54604,7 +54604,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
@@ -54618,26 +54618,26 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P197" t="n">
-        <v>34.8</v>
+        <v>30.6</v>
       </c>
       <c r="Q197" t="n">
-        <v>17.1</v>
+        <v>42.3</v>
       </c>
       <c r="R197" t="n">
         <v>27.6</v>
       </c>
       <c r="S197" t="n">
-        <v>92.09999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="T197" t="n">
         <v>50</v>
       </c>
       <c r="U197" t="n">
-        <v>3.4</v>
+        <v>58.1</v>
       </c>
       <c r="V197" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y197" t="inlineStr">
@@ -54693,27 +54693,27 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL197" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.6% barrel, 8.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
@@ -54723,104 +54723,104 @@
       </c>
       <c r="AN197" t="inlineStr">
         <is>
+          <t>8.67</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>38.54</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>88.34</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>99.0661</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>0.3653</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>0.1407</t>
+        </is>
+      </c>
+      <c r="AT197" t="inlineStr">
+        <is>
+          <t>0.2957</t>
+        </is>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>70.97</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>10.79</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>42.7</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>29.09</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>0.1529</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>44.95</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>90.37</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>101.3987</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>0.4373</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>0.1524</t>
-        </is>
-      </c>
-      <c r="AT197" t="inlineStr">
-        <is>
-          <t>0.3341</t>
-        </is>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>69.8</t>
-        </is>
-      </c>
-      <c r="AV197" t="inlineStr">
-        <is>
-          <t>13.74</t>
-        </is>
-      </c>
-      <c r="AW197" t="inlineStr">
-        <is>
-          <t>26.21</t>
-        </is>
-      </c>
-      <c r="AX197" t="inlineStr">
-        <is>
-          <t>23.51</t>
-        </is>
-      </c>
-      <c r="AY197" t="inlineStr">
-        <is>
-          <t>12.4</t>
-        </is>
-      </c>
-      <c r="AZ197" t="inlineStr">
-        <is>
-          <t>0.1349</t>
-        </is>
-      </c>
-      <c r="BA197" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
-      </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>40.29</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>89.15</t>
         </is>
       </c>
       <c r="BD197" t="inlineStr">
         <is>
-          <t>0.2768</t>
+          <t>0.4344</t>
         </is>
       </c>
       <c r="BE197" t="inlineStr">
         <is>
-          <t>0.0975</t>
+          <t>0.1685</t>
         </is>
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="BG197" t="inlineStr"/>
       <c r="BH197" t="inlineStr"/>
       <c r="BI197" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ197" t="inlineStr"/>
@@ -54831,27 +54831,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>642215</t>
+          <t>666182</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Weston Wilson</t>
+          <t>Bo Bichette</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-07-21T01:40:00Z</t>
+          <t>2026-07-20T23:40:00Z</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -54861,22 +54861,22 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Andrew Abbott</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>671096</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L198" t="n">
@@ -54894,26 +54894,26 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P198" t="n">
-        <v>24.8</v>
+        <v>34.8</v>
       </c>
       <c r="Q198" t="n">
-        <v>41.1</v>
+        <v>17.1</v>
       </c>
       <c r="R198" t="n">
-        <v>25.4</v>
+        <v>27.6</v>
       </c>
       <c r="S198" t="n">
-        <v>47.9</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T198" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U198" t="n">
-        <v>33.7</v>
+        <v>3.4</v>
       </c>
       <c r="V198" t="inlineStr">
         <is>
@@ -54927,7 +54927,7 @@
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
@@ -54969,27 +54969,27 @@
       </c>
       <c r="AH198" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/9, 1 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL198" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.8% barrel, 16.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.6% barrel, 8.7 HR allowed</t>
         </is>
       </c>
       <c r="AM198" t="inlineStr">
@@ -54999,104 +54999,104 @@
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>87.37</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>98.2744</t>
+          <t>101.3987</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>0.3374</t>
+          <t>0.4373</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1524</t>
         </is>
       </c>
       <c r="AT198" t="inlineStr">
         <is>
-          <t>0.2831</t>
+          <t>0.3341</t>
         </is>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>13.74</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>50.91</t>
+          <t>26.21</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>0.1367</t>
+          <t>0.1349</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>89.13</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="BD198" t="inlineStr">
         <is>
-          <t>0.4137</t>
+          <t>0.2768</t>
         </is>
       </c>
       <c r="BE198" t="inlineStr">
         <is>
-          <t>0.1632</t>
+          <t>0.0975</t>
         </is>
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>25.01</t>
         </is>
       </c>
       <c r="BG198" t="inlineStr"/>
       <c r="BH198" t="inlineStr"/>
       <c r="BI198" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ198" t="inlineStr"/>
@@ -55107,27 +55107,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>642215</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Weston Wilson</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-07-20T23:10:00Z</t>
+          <t>2026-07-21T01:40:00Z</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -55137,17 +55137,17 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Andrew Abbott</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>671096</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -55156,7 +55156,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>36.7</v>
+        <v>37.3</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -55174,22 +55174,22 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>27.4</v>
+        <v>24.8</v>
       </c>
       <c r="Q199" t="n">
-        <v>34.7</v>
+        <v>41.1</v>
       </c>
       <c r="R199" t="n">
-        <v>34.3</v>
+        <v>25.4</v>
       </c>
       <c r="S199" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T199" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U199" t="n">
-        <v>36</v>
+        <v>33.7</v>
       </c>
       <c r="V199" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -55245,27 +55245,27 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 2/9, 1 HR</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.9% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.8% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
@@ -55275,104 +55275,104 @@
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>100.1334</t>
+          <t>98.2744</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>0.3374</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>0.1265</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.2831</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>50.91</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>0.1472</t>
+          <t>0.1367</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>37.27</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.13</t>
         </is>
       </c>
       <c r="BD199" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.4137</t>
         </is>
       </c>
       <c r="BE199" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1632</t>
         </is>
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr"/>
       <c r="BH199" t="inlineStr"/>
       <c r="BI199" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ199" t="inlineStr"/>
@@ -75078,7 +75078,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -75111,7 +75111,7 @@
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>57.6</v>
+        <v>56.2</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -75172,7 +75172,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -76182,7 +76182,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -76215,7 +76215,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>97</v>
+        <v>94.7</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -76276,7 +76276,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
